--- a/artfynd/A 744-2026 artfynd.xlsx
+++ b/artfynd/A 744-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>131063900</v>
       </c>
       <c r="B3" t="n">
-        <v>91773</v>
+        <v>91776</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 744-2026 artfynd.xlsx
+++ b/artfynd/A 744-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131032534</v>
       </c>
       <c r="B2" t="n">
-        <v>83225</v>
+        <v>83226</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131063900</v>
       </c>
       <c r="B3" t="n">
-        <v>91776</v>
+        <v>91777</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>131063898</v>
       </c>
       <c r="B4" t="n">
-        <v>83225</v>
+        <v>83226</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>131066903</v>
       </c>
       <c r="B8" t="n">
-        <v>83217</v>
+        <v>83218</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>131066895</v>
       </c>
       <c r="B9" t="n">
-        <v>79002</v>
+        <v>79003</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>131066896</v>
       </c>
       <c r="B13" t="n">
-        <v>79002</v>
+        <v>79003</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>131066891</v>
       </c>
       <c r="B15" t="n">
-        <v>79269</v>
+        <v>79270</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>131063926</v>
       </c>
       <c r="B16" t="n">
-        <v>83091</v>
+        <v>83092</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>131066892</v>
       </c>
       <c r="B20" t="n">
-        <v>81230</v>
+        <v>81231</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
         <v>131066899</v>
       </c>
       <c r="B21" t="n">
-        <v>83091</v>
+        <v>83092</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 744-2026 artfynd.xlsx
+++ b/artfynd/A 744-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131032534</v>
       </c>
       <c r="B2" t="n">
-        <v>83226</v>
+        <v>83228</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131063900</v>
       </c>
       <c r="B3" t="n">
-        <v>91777</v>
+        <v>91779</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>131063898</v>
       </c>
       <c r="B4" t="n">
-        <v>83226</v>
+        <v>83228</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>131066884</v>
       </c>
       <c r="B5" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>131066903</v>
       </c>
       <c r="B8" t="n">
-        <v>83218</v>
+        <v>83220</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>131066895</v>
       </c>
       <c r="B9" t="n">
-        <v>79003</v>
+        <v>79005</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>131066878</v>
       </c>
       <c r="B10" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1617,7 +1617,7 @@
         <v>131066883</v>
       </c>
       <c r="B11" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>131066880</v>
       </c>
       <c r="B12" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>131066896</v>
       </c>
       <c r="B13" t="n">
-        <v>79003</v>
+        <v>79005</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>131066879</v>
       </c>
       <c r="B14" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>131066891</v>
       </c>
       <c r="B15" t="n">
-        <v>79270</v>
+        <v>79272</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>131063926</v>
       </c>
       <c r="B16" t="n">
-        <v>83092</v>
+        <v>83094</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>131066881</v>
       </c>
       <c r="B17" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>131066882</v>
       </c>
       <c r="B18" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>131066886</v>
       </c>
       <c r="B19" t="n">
-        <v>57073</v>
+        <v>57075</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>131066892</v>
       </c>
       <c r="B20" t="n">
-        <v>81231</v>
+        <v>81233</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
         <v>131066899</v>
       </c>
       <c r="B21" t="n">
-        <v>83092</v>
+        <v>83094</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         <v>131066876</v>
       </c>
       <c r="B22" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>131066877</v>
       </c>
       <c r="B23" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 744-2026 artfynd.xlsx
+++ b/artfynd/A 744-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131032534</v>
       </c>
       <c r="B2" t="n">
-        <v>83228</v>
+        <v>83229</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131063900</v>
       </c>
       <c r="B3" t="n">
-        <v>91779</v>
+        <v>91780</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>131063898</v>
       </c>
       <c r="B4" t="n">
-        <v>83228</v>
+        <v>83229</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>131066884</v>
       </c>
       <c r="B5" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>131066903</v>
       </c>
       <c r="B8" t="n">
-        <v>83220</v>
+        <v>83221</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>131066895</v>
       </c>
       <c r="B9" t="n">
-        <v>79005</v>
+        <v>79006</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>131066878</v>
       </c>
       <c r="B10" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1617,7 +1617,7 @@
         <v>131066883</v>
       </c>
       <c r="B11" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>131066880</v>
       </c>
       <c r="B12" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>131066896</v>
       </c>
       <c r="B13" t="n">
-        <v>79005</v>
+        <v>79006</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>131066879</v>
       </c>
       <c r="B14" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>131066891</v>
       </c>
       <c r="B15" t="n">
-        <v>79272</v>
+        <v>79273</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2138,10 +2138,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131063926</v>
+        <v>131066881</v>
       </c>
       <c r="B16" t="n">
-        <v>83094</v>
+        <v>57887</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2149,37 +2149,45 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Torsby kommun, Vrm</t>
+          <t>Färntjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>408603</v>
+        <v>408720</v>
       </c>
       <c r="R16" t="n">
-        <v>6702927</v>
+        <v>6703065</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2209,6 +2217,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2223,22 +2236,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131066881</v>
+        <v>131063926</v>
       </c>
       <c r="B17" t="n">
-        <v>57886</v>
+        <v>83095</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2246,45 +2259,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Färntjärnen, Vrm</t>
+          <t>Torsby kommun, Vrm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>408720</v>
+        <v>408603</v>
       </c>
       <c r="R17" t="n">
-        <v>6703065</v>
+        <v>6702927</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2314,11 +2319,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2333,12 +2333,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2348,7 +2348,7 @@
         <v>131066882</v>
       </c>
       <c r="B18" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>131066886</v>
       </c>
       <c r="B19" t="n">
-        <v>57075</v>
+        <v>57076</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>131066892</v>
       </c>
       <c r="B20" t="n">
-        <v>81233</v>
+        <v>81234</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
         <v>131066899</v>
       </c>
       <c r="B21" t="n">
-        <v>83094</v>
+        <v>83095</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         <v>131066876</v>
       </c>
       <c r="B22" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>131066877</v>
       </c>
       <c r="B23" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 744-2026 artfynd.xlsx
+++ b/artfynd/A 744-2026 artfynd.xlsx
@@ -2138,10 +2138,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131066881</v>
+        <v>131063926</v>
       </c>
       <c r="B16" t="n">
-        <v>57887</v>
+        <v>83095</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2149,45 +2149,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Färntjärnen, Vrm</t>
+          <t>Torsby kommun, Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>408720</v>
+        <v>408603</v>
       </c>
       <c r="R16" t="n">
-        <v>6703065</v>
+        <v>6702927</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2217,11 +2209,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2236,22 +2223,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131063926</v>
+        <v>131066881</v>
       </c>
       <c r="B17" t="n">
-        <v>83095</v>
+        <v>57887</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2259,37 +2246,45 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Torsby kommun, Vrm</t>
+          <t>Färntjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>408603</v>
+        <v>408720</v>
       </c>
       <c r="R17" t="n">
-        <v>6702927</v>
+        <v>6703065</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2319,6 +2314,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2333,12 +2333,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 744-2026 artfynd.xlsx
+++ b/artfynd/A 744-2026 artfynd.xlsx
@@ -2138,10 +2138,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131063926</v>
+        <v>131066881</v>
       </c>
       <c r="B16" t="n">
-        <v>83095</v>
+        <v>57887</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2149,37 +2149,45 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Torsby kommun, Vrm</t>
+          <t>Färntjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>408603</v>
+        <v>408720</v>
       </c>
       <c r="R16" t="n">
-        <v>6702927</v>
+        <v>6703065</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2209,6 +2217,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2223,22 +2236,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131066881</v>
+        <v>131063926</v>
       </c>
       <c r="B17" t="n">
-        <v>57887</v>
+        <v>83095</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2246,45 +2259,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Färntjärnen, Vrm</t>
+          <t>Torsby kommun, Vrm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>408720</v>
+        <v>408603</v>
       </c>
       <c r="R17" t="n">
-        <v>6703065</v>
+        <v>6702927</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2314,11 +2319,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2333,12 +2333,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 744-2026 artfynd.xlsx
+++ b/artfynd/A 744-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>131063900</v>
       </c>
       <c r="B3" t="n">
-        <v>91780</v>
+        <v>91781</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>131063898</v>
       </c>
       <c r="B4" t="n">
-        <v>83229</v>
+        <v>83230</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>131066884</v>
       </c>
       <c r="B5" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>131066903</v>
       </c>
       <c r="B8" t="n">
-        <v>83221</v>
+        <v>83222</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>131066895</v>
       </c>
       <c r="B9" t="n">
-        <v>79006</v>
+        <v>79007</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>131066878</v>
       </c>
       <c r="B10" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1617,7 +1617,7 @@
         <v>131066883</v>
       </c>
       <c r="B11" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>131066880</v>
       </c>
       <c r="B12" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>131066896</v>
       </c>
       <c r="B13" t="n">
-        <v>79006</v>
+        <v>79007</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>131066879</v>
       </c>
       <c r="B14" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>131066891</v>
       </c>
       <c r="B15" t="n">
-        <v>79273</v>
+        <v>79274</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2138,10 +2138,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131066881</v>
+        <v>131063926</v>
       </c>
       <c r="B16" t="n">
-        <v>57887</v>
+        <v>83096</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2149,45 +2149,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Färntjärnen, Vrm</t>
+          <t>Torsby kommun, Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>408720</v>
+        <v>408603</v>
       </c>
       <c r="R16" t="n">
-        <v>6703065</v>
+        <v>6702927</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2217,11 +2209,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2236,22 +2223,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131063926</v>
+        <v>131066881</v>
       </c>
       <c r="B17" t="n">
-        <v>83095</v>
+        <v>57888</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2259,37 +2246,45 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Torsby kommun, Vrm</t>
+          <t>Färntjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>408603</v>
+        <v>408720</v>
       </c>
       <c r="R17" t="n">
-        <v>6702927</v>
+        <v>6703065</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2319,6 +2314,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2333,12 +2333,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2348,7 +2348,7 @@
         <v>131066882</v>
       </c>
       <c r="B18" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>131066892</v>
       </c>
       <c r="B20" t="n">
-        <v>81234</v>
+        <v>81235</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
         <v>131066899</v>
       </c>
       <c r="B21" t="n">
-        <v>83095</v>
+        <v>83096</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         <v>131066876</v>
       </c>
       <c r="B22" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>131066877</v>
       </c>
       <c r="B23" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 744-2026 artfynd.xlsx
+++ b/artfynd/A 744-2026 artfynd.xlsx
@@ -1504,7 +1504,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131066878</v>
+        <v>131066883</v>
       </c>
       <c r="B10" t="n">
         <v>57888</v>
@@ -1547,10 +1547,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>408784</v>
+        <v>408727</v>
       </c>
       <c r="R10" t="n">
-        <v>6703105</v>
+        <v>6703044</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1614,7 +1614,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131066883</v>
+        <v>131066878</v>
       </c>
       <c r="B11" t="n">
         <v>57888</v>
@@ -1657,10 +1657,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>408727</v>
+        <v>408784</v>
       </c>
       <c r="R11" t="n">
-        <v>6703044</v>
+        <v>6703105</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -2138,10 +2138,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131063926</v>
+        <v>131066881</v>
       </c>
       <c r="B16" t="n">
-        <v>83096</v>
+        <v>57888</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2149,37 +2149,45 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Torsby kommun, Vrm</t>
+          <t>Färntjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>408603</v>
+        <v>408720</v>
       </c>
       <c r="R16" t="n">
-        <v>6702927</v>
+        <v>6703065</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2209,6 +2217,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2223,22 +2236,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131066881</v>
+        <v>131063926</v>
       </c>
       <c r="B17" t="n">
-        <v>57888</v>
+        <v>83096</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2246,45 +2259,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Färntjärnen, Vrm</t>
+          <t>Torsby kommun, Vrm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>408720</v>
+        <v>408603</v>
       </c>
       <c r="R17" t="n">
-        <v>6703065</v>
+        <v>6702927</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2314,11 +2319,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2333,12 +2333,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 744-2026 artfynd.xlsx
+++ b/artfynd/A 744-2026 artfynd.xlsx
@@ -2757,7 +2757,7 @@
         <v>131066876</v>
       </c>
       <c r="B22" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>131066877</v>
       </c>
       <c r="B23" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
